--- a/document/expr10/model_config.xlsx
+++ b/document/expr10/model_config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="14460"/>
   </bookViews>
   <sheets>
     <sheet name="model" sheetId="33" r:id="rId1"/>
@@ -4780,7 +4780,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10830" uniqueCount="795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10868" uniqueCount="799">
   <si>
     <t>no</t>
     <phoneticPr fontId="5"/>
@@ -17987,10 +17987,6 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t xml:space="preserve">#LGBMClasssifier 공식피쳐 + ip SG + class_weight O + learning rate=0.01  1개월단위 </t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
     <t>#LGBMClasssifier 공식피쳐 + ip SG + class_weight X + learning rate=0.01  1개월단위</t>
     <phoneticPr fontId="5"/>
   </si>
@@ -18003,7 +17999,27 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>20220603</t>
+    <t>20241104</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t xml:space="preserve">#en_nw_ext_25 + ip SG + learning rate=0.01  1개월단위 </t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>nw_ext_24</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t xml:space="preserve">#nw_ext_24 + ip SG + learning rate=0.01  1개월단위 </t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>#LGBMRanker 공식피쳐</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>20210604</t>
     <phoneticPr fontId="5"/>
   </si>
 </sst>
@@ -21847,7 +21863,7 @@
         <xdr:cNvPr id="2" name="Text Box 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0800-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -23145,7 +23161,7 @@
         <xdr:cNvPr id="60417" name="Text Box 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0900-000001EC0000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000001EC0000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -24681,30 +24697,30 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:T111"/>
-  <sheetFormatPr defaultRowHeight="17.5"/>
+  <dimension ref="A1:T115"/>
+  <sheetFormatPr defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="8.84375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="9.765625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" style="2" customWidth="1"/>
     <col min="3" max="3" width="10" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.07421875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.53515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.23046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" style="2" customWidth="1"/>
     <col min="7" max="7" width="10" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.765625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10.23046875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.84375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="7.53515625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="9.3046875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="11.07421875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="10.23046875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="9.69140625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="14.84375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="9.84375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="6.07421875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.77734375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.21875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="7.5546875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="9.33203125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="11.109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="10.21875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="9.6640625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="14.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="9.88671875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="6.109375" style="2" customWidth="1"/>
     <col min="19" max="19" width="8" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.765625" style="2" customWidth="1"/>
-    <col min="21" max="21" width="4.69140625" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="4.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1" ht="34.5" customHeight="1">
@@ -28607,7 +28623,7 @@
     </row>
     <row r="108" spans="1:20">
       <c r="A108" s="5" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B108" s="46"/>
       <c r="C108" s="46"/>
@@ -28676,7 +28692,7 @@
     </row>
     <row r="110" spans="1:20">
       <c r="A110" s="5" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
     </row>
     <row r="111" spans="1:20">
@@ -28684,10 +28700,10 @@
         <v>39104</v>
       </c>
       <c r="B111" s="46" t="s">
+        <v>792</v>
+      </c>
+      <c r="C111" s="46" t="s">
         <v>793</v>
-      </c>
-      <c r="C111" s="46" t="s">
-        <v>794</v>
       </c>
       <c r="D111" s="11" t="s">
         <v>108</v>
@@ -28702,7 +28718,7 @@
         <v>25</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="I111" s="2" t="s">
         <v>25</v>
@@ -28738,6 +28754,159 @@
         <v>1825</v>
       </c>
       <c r="T111" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="112" spans="1:20">
+      <c r="A112" s="5" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="113" spans="1:20">
+      <c r="A113" s="37">
+        <v>39106</v>
+      </c>
+      <c r="B113" s="46" t="s">
+        <v>792</v>
+      </c>
+      <c r="C113" s="46" t="s">
+        <v>793</v>
+      </c>
+      <c r="D113" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L113" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="M113" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N113" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O113" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P113" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q113" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R113" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="S113" s="2">
+        <v>1825</v>
+      </c>
+      <c r="T113" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="114" spans="1:20" s="47" customFormat="1">
+      <c r="A114" s="46" t="s">
+        <v>797</v>
+      </c>
+      <c r="B114" s="46"/>
+      <c r="C114" s="46"/>
+      <c r="D114" s="2"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
+      <c r="G114" s="2"/>
+      <c r="H114" s="2"/>
+      <c r="I114" s="2"/>
+      <c r="J114" s="2"/>
+      <c r="K114" s="2"/>
+      <c r="L114" s="46"/>
+      <c r="M114" s="46"/>
+      <c r="N114" s="46"/>
+      <c r="O114" s="2"/>
+      <c r="P114" s="2"/>
+      <c r="Q114" s="2"/>
+      <c r="R114" s="46"/>
+      <c r="S114" s="2"/>
+      <c r="T114" s="2"/>
+    </row>
+    <row r="115" spans="1:20" s="47" customFormat="1">
+      <c r="A115" s="15">
+        <v>40001</v>
+      </c>
+      <c r="B115" s="46" t="s">
+        <v>798</v>
+      </c>
+      <c r="C115" s="46" t="s">
+        <v>793</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L115" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="M115" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="N115" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="O115" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P115" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="Q115" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="R115" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="S115" s="2">
+        <v>1825</v>
+      </c>
+      <c r="T115" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -28753,16 +28922,16 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z132"/>
-  <sheetFormatPr defaultRowHeight="17.5"/>
+  <sheetFormatPr defaultRowHeight="17.25"/>
   <cols>
-    <col min="3" max="3" width="12.4609375" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="9" max="9" width="1.69140625" customWidth="1"/>
-    <col min="12" max="12" width="13.07421875" customWidth="1"/>
+    <col min="9" max="9" width="1.6640625" customWidth="1"/>
+    <col min="12" max="12" width="13.109375" customWidth="1"/>
     <col min="13" max="13" width="15" customWidth="1"/>
     <col min="18" max="18" width="2" customWidth="1"/>
-    <col min="21" max="21" width="14.07421875" customWidth="1"/>
-    <col min="22" max="22" width="13.07421875" customWidth="1"/>
+    <col min="21" max="21" width="14.109375" customWidth="1"/>
+    <col min="22" max="22" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -38089,7 +38258,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M51"/>
-  <sheetFormatPr defaultRowHeight="17.5"/>
+  <sheetFormatPr defaultRowHeight="17.25"/>
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1">
@@ -38483,12 +38652,12 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I122"/>
-  <sheetFormatPr defaultRowHeight="17.5"/>
+  <sheetFormatPr defaultRowHeight="17.25"/>
   <cols>
-    <col min="4" max="4" width="13.23046875" customWidth="1"/>
-    <col min="5" max="5" width="8.69140625" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
     <col min="8" max="8" width="9"/>
-    <col min="9" max="9" width="13.23046875" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -42131,25 +42300,25 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:Q78"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="8.84375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="9.765625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" style="2" customWidth="1"/>
     <col min="3" max="3" width="10" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.07421875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.77734375" style="2" customWidth="1"/>
     <col min="6" max="6" width="18" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.765625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" style="2" customWidth="1"/>
     <col min="8" max="8" width="13" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.84375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="13.3046875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.88671875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" style="2" customWidth="1"/>
     <col min="11" max="12" width="14" style="2" customWidth="1"/>
-    <col min="13" max="13" width="14.84375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="9.84375" style="2" customWidth="1"/>
-    <col min="15" max="15" width="6.07421875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="14.88671875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="9.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="6.109375" style="2" customWidth="1"/>
     <col min="16" max="16" width="8" style="2" customWidth="1"/>
-    <col min="17" max="17" width="8.765625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="4.69140625" customWidth="1"/>
+    <col min="17" max="17" width="8.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="4.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="34.5" customHeight="1">
@@ -44425,25 +44594,25 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="B1:AB63"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25"/>
   <cols>
     <col min="1" max="1" width="9" style="40"/>
     <col min="2" max="2" width="7" style="44" customWidth="1"/>
     <col min="3" max="3" width="7" style="103" customWidth="1"/>
-    <col min="4" max="4" width="7.69140625" style="103" customWidth="1"/>
-    <col min="5" max="5" width="7.3046875" style="103" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" style="103" customWidth="1"/>
+    <col min="5" max="5" width="7.33203125" style="103" customWidth="1"/>
     <col min="6" max="8" width="9" style="40"/>
-    <col min="9" max="9" width="11.3046875" style="40" customWidth="1"/>
-    <col min="10" max="10" width="9.4609375" style="40" customWidth="1"/>
-    <col min="11" max="11" width="7.765625" style="40" customWidth="1"/>
-    <col min="12" max="12" width="7.69140625" style="40" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" style="40" customWidth="1"/>
+    <col min="10" max="10" width="9.44140625" style="40" customWidth="1"/>
+    <col min="11" max="11" width="7.77734375" style="40" customWidth="1"/>
+    <col min="12" max="12" width="7.6640625" style="40" customWidth="1"/>
     <col min="13" max="15" width="9" style="40"/>
     <col min="16" max="18" width="0" style="40" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="0.765625" style="40" customWidth="1"/>
+    <col min="19" max="19" width="0.77734375" style="40" customWidth="1"/>
     <col min="20" max="25" width="9" style="40"/>
     <col min="26" max="28" width="0" style="40" hidden="1" customWidth="1"/>
     <col min="29" max="29" width="9" style="40"/>
-    <col min="30" max="30" width="9.4609375" style="40" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.44140625" style="40" bestFit="1" customWidth="1"/>
     <col min="31" max="16384" width="9" style="40"/>
   </cols>
   <sheetData>
@@ -44492,7 +44661,7 @@
       <c r="AA1" s="129"/>
       <c r="AB1" s="130"/>
     </row>
-    <row r="2" spans="2:28" s="1" customFormat="1" ht="53" thickBot="1">
+    <row r="2" spans="2:28" s="1" customFormat="1" ht="52.5" thickBot="1">
       <c r="B2" s="68" t="s">
         <v>540</v>
       </c>
@@ -47294,7 +47463,7 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultRowHeight="17.5"/>
+  <sheetFormatPr defaultRowHeight="17.25"/>
   <cols>
     <col min="3" max="3" width="9"/>
     <col min="5" max="6" width="9"/>
@@ -48175,29 +48344,29 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:T177"/>
-  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="17.5"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="8.84375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="9.765625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" style="2" customWidth="1"/>
     <col min="3" max="3" width="10" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.07421875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.53515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.23046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" style="2" customWidth="1"/>
     <col min="7" max="7" width="10" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7.765625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="6.69140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.84375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="7.53515625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="9.3046875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="11.07421875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="10.23046875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="9.69140625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="14.84375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="9.84375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="6.07421875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7.77734375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="6.6640625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="7.5546875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="9.33203125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="11.109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="10.21875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="9.6640625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="14.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="9.88671875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="6.109375" style="2" customWidth="1"/>
     <col min="19" max="19" width="8" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.765625" style="2" customWidth="1"/>
-    <col min="21" max="21" width="4.69140625" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="4.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1" ht="34.5" customHeight="1">
@@ -54616,25 +54785,25 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:Q176"/>
-  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="17.5"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="8.84375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="9.765625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" style="2" customWidth="1"/>
     <col min="3" max="3" width="10" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.07421875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.77734375" style="2" customWidth="1"/>
     <col min="6" max="6" width="18" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.765625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" style="2" customWidth="1"/>
     <col min="8" max="8" width="13" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.84375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="13.3046875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.88671875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" style="2" customWidth="1"/>
     <col min="11" max="12" width="14" style="2" customWidth="1"/>
-    <col min="13" max="13" width="14.84375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="9.84375" style="2" customWidth="1"/>
-    <col min="15" max="15" width="6.07421875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="14.88671875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="9.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="6.109375" style="2" customWidth="1"/>
     <col min="16" max="16" width="8" style="2" customWidth="1"/>
-    <col min="17" max="17" width="8.765625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="4.69140625" customWidth="1"/>
+    <col min="17" max="17" width="8.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="4.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="34.5" customHeight="1">
@@ -60066,28 +60235,28 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:V296"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="8.84375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="9.765625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" style="2" customWidth="1"/>
     <col min="3" max="3" width="10" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.07421875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.77734375" style="2" customWidth="1"/>
     <col min="6" max="6" width="18" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.765625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" style="2" customWidth="1"/>
     <col min="8" max="8" width="13" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.84375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="13.3046875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.88671875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" style="2" customWidth="1"/>
     <col min="11" max="12" width="14" style="2" customWidth="1"/>
-    <col min="13" max="13" width="14.84375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="9.84375" style="2" customWidth="1"/>
-    <col min="15" max="15" width="5.4609375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="9.4609375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="2.69140625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="1.07421875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="14.88671875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="9.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="5.44140625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="9.44140625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="2.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="1.109375" style="2" customWidth="1"/>
     <col min="19" max="19" width="8" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.765625" style="2" customWidth="1"/>
-    <col min="21" max="21" width="4.69140625" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="4.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1" ht="34.5" customHeight="1">
@@ -71644,10 +71813,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:EM181"/>
-  <sheetFormatPr defaultRowHeight="17.5"/>
+  <sheetFormatPr defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="17.07421875" customWidth="1"/>
-    <col min="5" max="5" width="11.07421875" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:130">
@@ -73195,9 +73364,9 @@
     <tabColor theme="1"/>
   </sheetPr>
   <dimension ref="A1:Z48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25"/>
   <cols>
-    <col min="9" max="9" width="1.69140625" customWidth="1"/>
+    <col min="9" max="9" width="1.6640625" customWidth="1"/>
     <col min="18" max="18" width="2" customWidth="1"/>
   </cols>
   <sheetData>
@@ -73212,7 +73381,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="35">
+    <row r="2" spans="1:26">
       <c r="A2" s="26" t="s">
         <v>244</v>
       </c>
@@ -73667,7 +73836,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="35">
+    <row r="12" spans="1:26" ht="34.5">
       <c r="A12" s="26" t="s">
         <v>244</v>
       </c>
